--- a/www/flightdata/xlsx/eoss-314.xlsx
+++ b/www/flightdata/xlsx/eoss-314.xlsx
@@ -3852,7 +3852,7 @@
         <v>29625.95</v>
       </c>
       <c r="I2">
-        <v>679</v>
+        <v>505</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
